--- a/6 sem/ТППО/Таблички лаб.1.xlsx
+++ b/6 sem/ТППО/Таблички лаб.1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>№</t>
   </si>
@@ -47,12 +47,6 @@
     <t>Информация о товаре</t>
   </si>
   <si>
-    <t>Информация о клиенте</t>
-  </si>
-  <si>
-    <t>Информация о  сотруднике</t>
-  </si>
-  <si>
     <t>Сотрудник</t>
   </si>
   <si>
@@ -81,6 +75,9 @@
   </si>
   <si>
     <t>Форма  на сайте</t>
+  </si>
+  <si>
+    <t>Информация о количестве товара</t>
   </si>
 </sst>
 </file>
@@ -426,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="1"/>
@@ -451,7 +448,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -465,19 +462,19 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" s="4">
         <v>2</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -488,49 +485,35 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -548,38 +531,52 @@
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>5</v>
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -587,52 +584,38 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -767,7 +750,6 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
@@ -824,17 +806,6 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
